--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DarkGambit\DataTable\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EE6AB9-DF00-46D3-9176-7A1E9703D24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB557D2-1845-4E9D-A551-DC931F249019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38430" windowHeight="10440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -243,6 +243,10 @@
   </si>
   <si>
     <t>relic_heart_of_the_beast</t>
+  </si>
+  <si>
+    <t>tetetettte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -642,7 +646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1069,6 +1073,11 @@
         <v>69</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DarkGambit\DataTable\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F806199-DCF1-4A54-8816-AD8B1B65384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49E0A64-2D70-406A-8D74-D4D78AFC6E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1785" windowWidth="38430" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attendance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="20">
   <si>
     <t>Icon_Common_Dia_S</t>
   </si>
@@ -85,6 +85,10 @@
   </si>
   <si>
     <t>Icon_Common_Gem_S</t>
+  </si>
+  <si>
+    <t>wdwdwdwdwdwd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -711,7 +715,9 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="9"/>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49E0A64-2D70-406A-8D74-D4D78AFC6E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F17648-EE7D-4D4F-81B6-F4EEE8DE25E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1785" windowWidth="38430" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29100" yWindow="3615" windowWidth="38430" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attendance" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
     <t>Icon_Common_Gem_S</t>
   </si>
   <si>
-    <t>wdwdwdwdwdwd</t>
+    <t>wdwdwdwdwfvfvfvfvfvfvfvdwd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F17648-EE7D-4D4F-81B6-F4EEE8DE25E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC177B5-FFE1-4527-BC7C-6A08980B3994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29100" yWindow="3615" windowWidth="38430" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2340" windowWidth="38430" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attendance" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
     <t>Icon_Common_Gem_S</t>
   </si>
   <si>
-    <t>wdwdwdwdwfvfvfvfvfvfvfvdwd</t>
+    <t>sss</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DarkGambit\DataTable\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6083B16F-A39E-48E0-B165-D8DF447A6B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A62EE5-7A4B-4500-96BF-2A4071C5E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="1380" windowWidth="38430" windowHeight="17085" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11805" yWindow="5160" windowWidth="38430" windowHeight="10440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
   <si>
     <t>idx</t>
   </si>
@@ -477,6 +477,10 @@
   </si>
   <si>
     <t>seed_vessel</t>
+  </si>
+  <si>
+    <t>wdwdwdwdw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -963,7 +967,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1395,6 +1399,11 @@
       </c>
       <c r="M11" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A62EE5-7A4B-4500-96BF-2A4071C5E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FC015C-8EE2-4233-BB2A-411DE5C37F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11805" yWindow="5160" windowWidth="38430" windowHeight="10440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
     <t>seed_vessel</t>
   </si>
   <si>
-    <t>wdwdwdwdw</t>
+    <t>wdwdwdwdwwwww</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FC015C-8EE2-4233-BB2A-411DE5C37F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89D58DB-B937-47C3-819D-93EAD202C219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13740" yWindow="4785" windowWidth="38430" windowHeight="12780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
   <si>
     <t>idx</t>
   </si>
@@ -477,10 +477,6 @@
   </si>
   <si>
     <t>seed_vessel</t>
-  </si>
-  <si>
-    <t>wdwdwdwdwwwww</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1402,8 +1398,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>146</v>
+      <c r="B12" s="4">
+        <v>22222</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89D58DB-B937-47C3-819D-93EAD202C219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BC2DA-C582-4A5B-9287-2E161B8D427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="4785" windowWidth="38430" windowHeight="12780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>22222</v>
+        <v>333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BC2DA-C582-4A5B-9287-2E161B8D427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0D4861-58A0-49BA-9F68-1F38EF9C6A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
   <si>
     <t>idx</t>
   </si>
@@ -477,6 +477,10 @@
   </si>
   <si>
     <t>seed_vessel</t>
+  </si>
+  <si>
+    <t>jjjjjjjjj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1398,8 +1402,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
-        <v>333333333333</v>
+      <c r="B12" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BC2DA-C582-4A5B-9287-2E161B8D427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC46F63-050D-41E5-8C6A-4FC289CEEEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
   <si>
     <t>idx</t>
   </si>
@@ -477,6 +477,10 @@
   </si>
   <si>
     <t>seed_vessel</t>
+  </si>
+  <si>
+    <t>jjjkkkk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1398,8 +1402,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
-        <v>333333333333</v>
+      <c r="B12" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC46F63-050D-41E5-8C6A-4FC289CEEEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED51D19A-B5ED-4965-97E3-FC2B2741162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
   <si>
     <t>idx</t>
   </si>
@@ -477,10 +477,6 @@
   </si>
   <si>
     <t>seed_vessel</t>
-  </si>
-  <si>
-    <t>jjjkkkk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1402,8 +1398,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>146</v>
+      <c r="B12" s="4">
+        <v>222222222222</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC46F63-050D-41E5-8C6A-4FC289CEEEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F472A226-390E-43FA-80C4-F59785EE69A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="146">
   <si>
     <t>idx</t>
   </si>
@@ -477,10 +477,6 @@
   </si>
   <si>
     <t>seed_vessel</t>
-  </si>
-  <si>
-    <t>jjjkkkk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1402,8 +1398,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>146</v>
+      <c r="B12" s="4">
+        <v>3333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED51D19A-B5ED-4965-97E3-FC2B2741162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22715AE4-6BD8-4FB1-B848-CDCC3C6AA80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>222222222222</v>
+        <v>1111111111111</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F472A226-390E-43FA-80C4-F59785EE69A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD6390D-5F93-4677-9A10-5EB65835C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>3333333333333</v>
+        <v>22222222222</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22715AE4-6BD8-4FB1-B848-CDCC3C6AA80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B7CE0A-721B-4556-B0AB-3F836E2CF473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>1111111111111</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD6390D-5F93-4677-9A10-5EB65835C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF90D7D7-5AEE-4014-A5B2-13BCFBD97843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>22222222222</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF90D7D7-5AEE-4014-A5B2-13BCFBD97843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF21166F-4380-44A1-BA23-D1E5CB413E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>22</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>

--- a/DT_DW_Artifact.xlsx
+++ b/DT_DW_Artifact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\git_test_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF90D7D7-5AEE-4014-A5B2-13BCFBD97843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51806D7D-F2D7-422E-99F4-8D5581B665B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="0" windowWidth="38430" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>22</v>
+        <v>2222</v>
       </c>
     </row>
   </sheetData>
